--- a/employee_surveys/046_hr_process_experience_survey--employee_surveys.xlsx
+++ b/employee_surveys/046_hr_process_experience_survey--employee_surveys.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,12 +437,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="34" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -520,18 +520,18 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>form_title</t>
+          <t>overall_experience</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>HR Process Experience Survey</t>
+          <t>Overall Experience</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -543,18 +543,18 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>category</t>
+          <t>hr_effectiveness</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>category</t>
+          <t>Effectiveness of HR Department</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -566,179 +566,179 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>description</t>
+          <t>adequate_support</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>description</t>
+          <t>Adequate Support</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>email</t>
+          <t>timely_responses</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>Timeliness of Responses</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>phone</t>
+          <t>training</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Phone</t>
+          <t>Sufficient Training</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>approachability</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Date</t>
+          <t>Approachability</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>quality_service</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Time</t>
+          <t>Quality of Service</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>efficiency_process</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Note</t>
+          <t>Efficiency of HR Processes</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>employee_surveys_1</t>
+          <t>contact_outside_work_hours</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Employee Surveys</t>
+          <t>Contact HR outside of Work Hours</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>form_comments</t>
+          <t>proactive_approach</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Comments</t>
+          <t>Proactive Approach</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -750,18 +750,18 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>form_title_2</t>
+          <t>challenges</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>HR Process Experience Survey</t>
+          <t>Major Challenge</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -773,18 +773,18 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>category_1</t>
+          <t>meet_expectations</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Category</t>
+          <t>Meet Expectations</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -796,12 +796,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>description_1</t>
+          <t>suggestions</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Description</t>
+          <t>Suggestions</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -814,17 +814,17 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>email_1</t>
+          <t>transparency</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>Transparency</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -837,17 +837,17 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>phone_1</t>
+          <t>approachability_2</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Phone</t>
+          <t>Approachability 2</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -860,17 +860,17 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>date_1</t>
+          <t>resources</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Date</t>
+          <t>Resources</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -883,17 +883,17 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>time_1</t>
+          <t>recommend</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Time</t>
+          <t>Would Recommend</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -906,182 +906,21 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>note_1</t>
+          <t>overall_experience_2</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Note</t>
+          <t>Overall Experience 2</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>employee_surveys_1_1</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Employee Surveys 1</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>employee_surveys_1_2</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Employee Surveys 2</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>form_comments_1</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Comments</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>question_1</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Question 1</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>question_2</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Question 2</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>question_3</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Question 3</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>submitted_by</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Submitted By</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1098,12 +937,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C13"/>
+  <dimension ref="A1:C29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="6" customWidth="1" min="2" max="2"/>
-    <col width="7" customWidth="1" min="3" max="3"/>
+    <col width="36" customWidth="1" min="1" max="1"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1126,204 +965,476 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>category_choices</t>
+          <t>hr_effectiveness_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>excellent</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Excellent</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>category_choices</t>
+          <t>hr_effectiveness_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>good</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Good</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>employee_surveys_1_choices</t>
+          <t>hr_effectiveness_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>fair</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Fair</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>employee_surveys_1_choices</t>
+          <t>hr_effectiveness_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>bad</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Bad</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>category_1_choices</t>
+          <t>timely_responses_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>category_1_choices</t>
+          <t>timely_responses_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>employee_surveys_1_1_choices</t>
+          <t>training_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>employee_surveys_1_1_choices</t>
+          <t>training_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>employee_surveys_1_2_choices</t>
+          <t>approachability_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>employee_surveys_1_2_choices</t>
+          <t>approachability_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>submitted_by_choices</t>
+          <t>quality_service_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>excellent</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Excellent</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>submitted_by_choices</t>
+          <t>quality_service_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>good</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Good</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>quality_service_choices</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>fair</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Fair</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>quality_service_choices</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>bad</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Bad</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>contact_outside_work_hours_choices</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>contact_outside_work_hours_choices</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>proactive_approach_choices</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>proactive_approach_choices</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>meet_expectations_choices</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>meet_expectations_choices</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>transparency_choices</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>transparency_choices</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>approachability_2_choices</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>approachability_2_choices</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>resources_choices</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>resources_choices</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>recommend_choices</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>recommend_choices</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>False</t>
         </is>
       </c>
     </row>
